--- a/momentum/Sharpe Score/n500_rankings.xlsx
+++ b/momentum/Sharpe Score/n500_rankings.xlsx
@@ -32,35 +32,35 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFC840"/>
+      <color rgb="001A365D"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0000CCFF"/>
+      <color rgb="000055CC"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="00E0E0F0"/>
+      <color rgb="00111111"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="007070A0"/>
+      <color rgb="00707070"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0000E5A0"/>
+      <color rgb="00137333"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FF4466"/>
+      <color rgb="00C5221F"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -73,37 +73,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000A0A18"/>
+        <fgColor rgb="00F0F4F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E2A4A"/>
+        <fgColor rgb="00E8EEF2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000D0D14"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00003322"/>
+        <fgColor rgb="00E6F4EA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0013131F"/>
+        <fgColor rgb="00F8F9FA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00330011"/>
+        <fgColor rgb="00FCE8E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001A0A0A"/>
+        <fgColor rgb="00F0F0F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -117,16 +117,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00333355"/>
+        <color rgb="00CCCCCC"/>
       </left>
       <right style="thin">
-        <color rgb="00333355"/>
+        <color rgb="00CCCCCC"/>
       </right>
       <top style="thin">
-        <color rgb="00333355"/>
+        <color rgb="00CCCCCC"/>
       </top>
       <bottom style="thin">
-        <color rgb="00333355"/>
+        <color rgb="00CCCCCC"/>
       </bottom>
     </border>
   </borders>
@@ -138,7 +138,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
